--- a/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré. Il dit : je suis inquiet. La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte. Il dit : le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là. Gérard raconte encore. Il dit : je suis inquiet. Maman dit : tu as bien raconté. On rejoint un adulte. On raconte. Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
+          <t>Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré. Je suis inquiet. La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte. Le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là. Gérard raconte encore. Je suis inquiet. Tu as bien raconté. On rejoint un adulte. On raconte. Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré.
+narrateur|Je suis inquiet.
+narrateur|La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte.
+narrateur|Le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là.
+narrateur|Gérard raconte encore.
+narrateur|Je suis inquiet.
+maman|Tu as bien raconté. On rejoint un adulte. On raconte.
+narrateur|Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gérard est inquiet. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gérard a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gérard s'assoit. La pluie tombe dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1514,7 @@
           <t>narrateur|Gérard est inquiet. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1686,7 @@
           <t>narrateur|Gérard a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Gérard s'assoit. La pluie tombe dehors.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gérard raconte qu'il est inquiet</t>
+          <t>Amir raconte le tonnerre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le linge danse. Le ciel grisonne. Amir a le ventre serré. Il raconte à papa, puis à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré. Je suis inquiet. La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte. Le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là. Gérard raconte encore. Je suis inquiet. Tu as bien raconté. On rejoint un adulte. On raconte. Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
+          <t>Le linge danse un peu sur le fil. Un t-shirt bleu s'envole, puis revient. La terre du jardin est encore chaude. Elle sent l'herbe coupée. Une abeille va d'une fleur à l'autre. Elle fait un bruit tout fin. Le linge sèche bien, Amir. Le t-shirt bleu danse. Oui. Il va rentrer bientôt. Un arrosoir vert attend près des tomates. Une goutte brille sur une feuille. Tu as vu la goutte, Amir ? Elle brille. Comme une petite perle. En ce moment, Amir est au jardin. Il touche la terre chaude du bout des doigts. Elle est tiède, papa. Oui. Le soleil l'a chauffée. Le ciel devient gris, tout doucement. Le linge s'arrête de danser. Un tonnerre gronde, loin d'abord. Puis un peu plus près. Le ventre d'Amir se serre. C'est un nœud tout dur. Je suis inquiet. Le bruit me serre le ventre. Tu peux venir, Amir. Amir va vers papa. Papa est l'adulte près de l'arrosoir. Le tonnerre me serre le ventre. Tu es inquiet. Tu as bien raconté. On rentre dans la cuisine. Je vous écoute. Ils vont dans la cuisine. La table sent le citron. Une carafe d'eau attend au milieu. Je suis inquiet. Le tonnerre a grogné. Tu as bien raconté. On rejoint un adulte. On raconte. Bravo, Amir. C'est du bon travail. Tu veux un peu d'eau ? Oui, maman. Amir boit de l'eau. Son ventre se desserre un peu. Parce que tu as raconté. Tu te sens moins seul. Ma main est sur ton épaule. J'ai raconté à l'adulte. Oui. À papa. Et à moi. La pluie commence sur le toit. Elle fait un bruit doux, maintenant. Le linge va rentrer plus tard. Toi, tu es ici. Tu restes près de la table ? Oui. Près de vous. La carafe cliquette tout bas. Le citron sent encore frais.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,19 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré.
-narrateur|Je suis inquiet.
-narrateur|La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte.
-narrateur|Le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là.
-narrateur|Gérard raconte encore.
-narrateur|Je suis inquiet.
-maman|Tu as bien raconté. On rejoint un adulte. On raconte.
-narrateur|Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.</t>
+          <t>narrateur|Le linge danse un peu sur le fil.
+narrateur|Un t-shirt bleu s'envole, puis revient.
+narrateur|La terre du jardin est encore chaude.
+narrateur|Elle sent l'herbe coupée.
+narrateur|Une abeille va d'une fleur à l'autre.
+narrateur|Elle fait un bruit tout fin.
+papa|Le linge sèche bien, Amir.
+enfant-m|Le t-shirt bleu danse.
+maman|Oui.
+maman|Il va rentrer bientôt.
+narrateur|Un arrosoir vert attend près des tomates.
+narrateur|Une goutte brille sur une feuille.
+papa|Tu as vu la goutte, Amir ?
+enfant-m|Elle brille.
+maman|Comme une petite perle.
+narrateur|En ce moment, Amir est au jardin.
+narrateur|Il touche la terre chaude du bout des doigts.
+enfant-m|Elle est tiède, papa.
+papa|Oui.
+papa|Le soleil l'a chauffée.
+narrateur|Le ciel devient gris, tout doucement.
+narrateur|Le linge s'arrête de danser.
+narrateur|Un tonnerre gronde, loin d'abord.
+narrateur|Puis un peu plus près.
+narrateur|Le ventre d'Amir se serre.
+narrateur|C'est un nœud tout dur.
+enfant-m|Je suis inquiet.
+enfant-m|Le bruit me serre le ventre.
+papa|Tu peux venir, Amir.
+narrateur|Amir va vers papa.
+narrateur|Papa est l'adulte près de l'arrosoir.
+enfant-m|Le tonnerre me serre le ventre.
+papa|Tu es inquiet.
+papa|Tu as bien raconté.
+papa|On rentre dans la cuisine.
+maman|Je vous écoute.
+narrateur|Ils vont dans la cuisine.
+narrateur|La table sent le citron.
+narrateur|Une carafe d'eau attend au milieu.
+enfant-m|Je suis inquiet.
+enfant-m|Le tonnerre a grogné.
+maman|Tu as bien raconté.
+maman|On rejoint un adulte.
+maman|On raconte.
+maman|Bravo, Amir.
+maman|C'est du bon travail.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Amir boit de l'eau.
+narrateur|Son ventre se desserre un peu.
+papa|Parce que tu as raconté.
+papa|Tu te sens moins seul.
+papa|Ma main est sur ton épaule.
+enfant-m|J'ai raconté à l'adulte.
+maman|Oui.
+maman|À papa.
+maman|Et à moi.
+narrateur|La pluie commence sur le toit.
+narrateur|Elle fait un bruit doux, maintenant.
+papa|Le linge va rentrer plus tard.
+maman|Toi, tu es ici.
+maman|Tu restes près de la table ?
+enfant-m|Oui.
+enfant-m|Près de vous.
+narrateur|La carafe cliquette tout bas.
+narrateur|Le citron sent encore frais.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>tonnerre_loin,pluie_jardin</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gérard est inquiet. Que fait-il ?</t>
+          <t>Amir est inquiet. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1511,7 +1581,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gérard est inquiet. Que fait-il ?</t>
+          <t>narrateur|Amir est inquiet.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1539,7 +1610,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gérard a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman.</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman. Bravo, Amir. Tu as raconté. C'est du bon travail. J'étais inquiet. J'ai raconté le tonnerre. Oui. Vers un adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,7 +1754,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gérard a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman.</t>
+          <t>narrateur|Amir a nommé : inquiet.
+narrateur|Il a rejoint un adulte.
+narrateur|Il a raconté à papa et maman.
+papa|Bravo, Amir.
+maman|Tu as raconté.
+maman|C'est du bon travail.
+enfant-m|J'étais inquiet.
+enfant-m|J'ai raconté le tonnerre.
+papa|Oui.
+papa|Vers un adulte.
+maman|Tu as le ventre plus doux ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1711,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gérard s'assoit. La pluie tombe dehors.</t>
+          <t>Amir s'assoit. La pluie tombe dehors. On écoute la pluie ? Oui. Elle chante sur le toit. Le jardin boit l'eau. L'arrosoir vert reste près des tomates. Le t-shirt bleu attend sous le fil. Tu restes à table ? Oui. Près de vous. On reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1929,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gérard s'assoit. La pluie tombe dehors.</t>
+          <t>narrateur|Amir s'assoit.
+narrateur|La pluie tombe dehors.
+maman|On écoute la pluie ?
+enfant-m|Oui.
+enfant-m|Elle chante sur le toit.
+papa|Le jardin boit l'eau.
+narrateur|L'arrosoir vert reste près des tomates.
+narrateur|Le t-shirt bleu attend sous le fil.
+maman|Tu restes à table ?
+enfant-m|Oui.
+enfant-m|Près de vous.
+papa|On reste.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. Tu as fait du bon travail. La pluie chante encore sur le toit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|J'étais inquiet.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La pluie chante encore sur le toit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le linge danse un peu sur le fil. Un t-shirt bleu s'envole, puis revient. La terre du jardin est encore chaude. Elle sent l'herbe coupée. Une abeille va d'une fleur à l'autre. Elle fait un bruit tout fin. Le linge sèche bien, Amir. Le t-shirt bleu danse. Oui. Il va rentrer bientôt. Un arrosoir vert attend près des tomates. Une goutte brille sur une feuille. Tu as vu la goutte, Amir ? Elle brille. Comme une petite perle. En ce moment, Amir est au jardin. Il touche la terre chaude du bout des doigts. Elle est tiède, papa. Oui. Le soleil l'a chauffée. Le ciel devient gris, tout doucement. Le linge s'arrête de danser. Un tonnerre gronde, loin d'abord. Puis un peu plus près. Le ventre d'Amir se serre. C'est un nœud tout dur. Je suis inquiet. Le bruit me serre le ventre. Tu peux venir, Amir. Amir va vers papa. Papa est l'adulte près de l'arrosoir. Le tonnerre me serre le ventre. Tu es inquiet. Tu as bien raconté. On rentre dans la cuisine. Je vous écoute. Ils vont dans la cuisine. La table sent le citron. Une carafe d'eau attend au milieu. Je suis inquiet. Le tonnerre a grogné. Tu as bien raconté. On rejoint un adulte. On raconte. Bravo, Amir. C'est du bon travail. Tu veux un peu d'eau ? Oui, maman. Amir boit de l'eau. Son ventre se desserre un peu. Parce que tu as raconté. Tu te sens moins seul. Ma main est sur ton épaule. J'ai raconté à l'adulte. Oui. À papa. Et à moi. La pluie commence sur le toit. Elle fait un bruit doux, maintenant. Le linge va rentrer plus tard. Toi, tu es ici. Tu restes près de la table ? Oui. Près de vous. La carafe cliquette tout bas. Le citron sent encore frais.</t>
+          <t>Le linge danse un peu sur le fil. Un t-shirt bleu s'envole, puis revient. La terre du jardin est encore chaude. Elle sent l'herbe coupée. Une abeille va d'une fleur à l'autre. Elle fait un bruit tout fin. Le linge sèche bien, Amir. Le t-shirt bleu danse. Oui. Il va rentrer bientôt. Un arrosoir vert attend près des tomates. Une goutte brille sur une feuille. Tu as vu la goutte, Amir ? Elle brille. Comme une petite perle. En ce moment, Amir est au jardin. Il touche la terre chaude du bout des doigts. Elle est tiède, papa. Oui. Le soleil l'a chauffée. Le ciel devient gris, tout doucement. Le linge s'arrête de danser. Un tonnerre gronde, loin d'abord. Puis un peu plus près. Le ventre d'Amir se serre. C'est un nœud tout dur. Je suis inquiet. Le bruit me serre le ventre. Tu peux venir, Amir. Amir va vers papa. Papa est l'adulte près de l'arrosoir. Le tonnerre me serre le ventre. Tu es inquiet. Tu as bien raconté. On rentre dans la cuisine. Je vous écoute. Ils vont dans la cuisine. La table sent le citron. Une carafe d'eau attend au milieu. Je suis inquiet. Le tonnerre a grogné. Tu as bien raconté. On rejoint un adulte. On raconte. Bravo, Amir. Tu veux un peu d'eau ? Oui, maman. Amir boit de l'eau. Son ventre se desserre un peu. Parce que tu as raconté. Tu te sens moins seul. Ma main est sur ton épaule. J'ai raconté à l'adulte. Oui. À papa. Et à moi. La pluie commence sur le toit. Elle fait un bruit doux, maintenant. Le linge va rentrer plus tard. Toi, tu es ici. Tu restes près de la table ? Oui. Près de vous. La carafe cliquette tout bas. Le citron sent encore frais.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gérard est au jardin. Le ciel devient gris. Un tonnerre gronde. Gérard sent son ventre serré. Il dit : je suis &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. La cause, c'est le bruit. Gérard va vers papa. Papa, c'est l'adulte. Gérard raconte. Il dit : le tonnerre me serre le ventre. Papa écoute. Ils vont dans la cuisine. Maman est là. Gérard raconte encore. Il dit : je suis inquiet. Maman dit : tu as bien raconté. On rejoint un adulte. On raconte. Gérard boit de l'eau. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Papa pose la main sur son épaule.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le linge danse un peu sur le fil. Un t-shirt bleu s'envole, puis revient. La terre du jardin est encore chaude. Elle sent l'herbe coupée. Une abeille va d'une fleur à l'autre. Elle fait un bruit tout fin. Le linge sèche bien, Amir. Le t-shirt bleu danse. Oui. Il va rentrer bientôt. Un arrosoir vert attend près des tomates. Une goutte brille sur une feuille. Tu as vu la goutte, Amir ? Elle brille. Comme une petite perle. En ce moment, Amir est au jardin. Il touche la terre chaude du bout des doigts. Elle est tiède, papa. Oui. Le soleil l'a chauffée. Le ciel devient gris, tout doucement. Le linge s'arrête de danser. Un tonnerre gronde, loin d'abord. Puis un peu plus près. Le ventre d'Amir se serre. C'est un nœud tout dur. Je suis inquiet. Le bruit me serre le ventre. Tu peux venir, Amir. Amir va vers papa. Papa est l'adulte près de l'arrosoir. Le tonnerre me serre le ventre. Tu es inquiet. Tu as bien raconté. On rentre dans la cuisine. Je vous écoute. Ils vont dans la cuisine. La table sent le citron. Une carafe d'eau attend au milieu. Je suis inquiet. Le tonnerre a grogné. Tu as bien raconté. On rejoint un adulte. On raconte. Bravo, Amir. Tu veux un peu d'eau ? Oui, maman. Amir boit de l'eau. Son ventre se desserre un peu. Parce que tu as raconté. Tu te sens moins seul. Ma main est sur ton épaule. J'ai raconté à l'adulte. Oui. À papa. Et à moi. La pluie commence sur le toit. Elle fait un bruit doux, maintenant. Le linge va rentrer plus tard. Toi, tu es ici. Tu restes près de la table ? Oui. Près de vous. La carafe cliquette tout bas. Le citron sent encore frais.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 maman|On rejoint un adulte.
 maman|On raconte.
 maman|Bravo, Amir.
-maman|C'est du bon travail.
 maman|Tu veux un peu d'eau ?
 enfant-m|Oui, maman.
 narrateur|Amir boit de l'eau.
@@ -1426,7 +1425,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gérard est &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est inquiet. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,7 +1584,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,12 +1608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman. Bravo, Amir. Tu as raconté. C'est du bon travail. J'étais inquiet. J'ai raconté le tonnerre. Oui. Vers un adulte. Tu as le ventre plus doux ? Oui, maman.</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman. Bravo, Amir. Tu as raconté. J'étais inquiet. J'ai raconté le tonnerre. Oui. Vers un adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gérard a nommé : &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Il a rejoint un adulte. Il a raconté à papa et maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a raconté à papa et maman. Bravo, Amir. Tu as raconté. J'étais inquiet. J'ai raconté le tonnerre. Oui. Vers un adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1757,6 @@
 narrateur|Il a raconté à papa et maman.
 papa|Bravo, Amir.
 maman|Tu as raconté.
-maman|C'est du bon travail.
 enfant-m|J'étais inquiet.
 enfant-m|J'ai raconté le tonnerre.
 papa|Oui.
@@ -1768,7 +1765,6 @@
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1798,7 +1794,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gérard s'assoit. La pluie tombe dehors.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir s'assoit. La pluie tombe dehors. On écoute la pluie ? Oui. Elle chante sur le toit. Le jardin boit l'eau. L'arrosoir vert reste près des tomates. Le t-shirt bleu attend sous le fil. Tu restes à table ? Oui. Près de vous. On reste.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1939,6 @@
 papa|On reste.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. J'étais inquiet. Bravo. Tu as fait du bon travail. La pluie chante encore sur le toit. L'histoire est finie.</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. La pluie chante encore sur le toit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. La pluie chante encore sur le toit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2106,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|J'étais inquiet.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|La pluie chante encore sur le toit.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La pluie chante encore sur le toit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gérard, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
